--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Read6c8c0b14d4b89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R5aad6d476de24673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd1bae0b1a3de47fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R93240a23de194477"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd1bae0b1a3de47fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R93240a23de194477"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66ade586ed4b4841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rd30806c3b9ab400a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66ade586ed4b4841"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rd30806c3b9ab400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R600a5aa3bc8c47b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R72c629f7de5c46b9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R600a5aa3bc8c47b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R72c629f7de5c46b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7662197d675f4fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rb0af3cd2d23b4f29"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7662197d675f4fb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rb0af3cd2d23b4f29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f35fde71c3b4329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rd673b77796444368"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f35fde71c3b4329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rd673b77796444368"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2cc74af6bf644849"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rb7b02f7bfe6b4502"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2cc74af6bf644849"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rb7b02f7bfe6b4502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4acf7923ca7946b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R9a50b35b44a14c1e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4acf7923ca7946b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R9a50b35b44a14c1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82902ffff6d04bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R8ff38064696e4fbc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82902ffff6d04bda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R8ff38064696e4fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R287b537c4818431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R710fd4da30974074"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R287b537c4818431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R710fd4da30974074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7c89fbe56ece4f4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rff144d89a84c4646"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7c89fbe56ece4f4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rff144d89a84c4646"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re67e01cab5be4a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R816f4d4540b04293"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re67e01cab5be4a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R816f4d4540b04293"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R662a233b2d9a4d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rc0d771c1e53940fe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R662a233b2d9a4d82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rc0d771c1e53940fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rea82ba41a86640c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rb29fdcac545e49cc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rea82ba41a86640c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rb29fdcac545e49cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d794a01a85d4bd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R2766ca62af674bce"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d794a01a85d4bd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R2766ca62af674bce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85cb942588534fdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rae797d373aba4651"/>
   </x:sheets>
 </x:workbook>
 </file>
